--- a/artfynd/A 11288-2024 artfynd.xlsx
+++ b/artfynd/A 11288-2024 artfynd.xlsx
@@ -1541,7 +1541,7 @@
         <v>116929266</v>
       </c>
       <c r="B10" t="n">
-        <v>57945</v>
+        <v>58000</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11288-2024 artfynd.xlsx
+++ b/artfynd/A 11288-2024 artfynd.xlsx
@@ -1541,7 +1541,7 @@
         <v>116929266</v>
       </c>
       <c r="B10" t="n">
-        <v>58000</v>
+        <v>58013</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11288-2024 artfynd.xlsx
+++ b/artfynd/A 11288-2024 artfynd.xlsx
@@ -1541,7 +1541,7 @@
         <v>116929266</v>
       </c>
       <c r="B10" t="n">
-        <v>58013</v>
+        <v>58015</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11288-2024 artfynd.xlsx
+++ b/artfynd/A 11288-2024 artfynd.xlsx
@@ -1567,11 +1567,7 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Holmensbäcken, Holmensbäcken, Mpd</t>

--- a/artfynd/A 11288-2024 artfynd.xlsx
+++ b/artfynd/A 11288-2024 artfynd.xlsx
@@ -1541,7 +1541,7 @@
         <v>116929266</v>
       </c>
       <c r="B10" t="n">
-        <v>58015</v>
+        <v>58025</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11288-2024 artfynd.xlsx
+++ b/artfynd/A 11288-2024 artfynd.xlsx
@@ -1541,7 +1541,7 @@
         <v>116929266</v>
       </c>
       <c r="B10" t="n">
-        <v>58025</v>
+        <v>58026</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11288-2024 artfynd.xlsx
+++ b/artfynd/A 11288-2024 artfynd.xlsx
@@ -1541,7 +1541,7 @@
         <v>116929266</v>
       </c>
       <c r="B10" t="n">
-        <v>58026</v>
+        <v>58027</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11288-2024 artfynd.xlsx
+++ b/artfynd/A 11288-2024 artfynd.xlsx
@@ -1541,7 +1541,7 @@
         <v>116929266</v>
       </c>
       <c r="B10" t="n">
-        <v>58027</v>
+        <v>58030</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
